--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256458311</v>
+        <v>46157.93085654662</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93085654662</v>
+        <v>46157.93163915011</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93163915011</v>
+        <v>46157.93396636528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93396636528</v>
+        <v>46157.93714194732</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93714194732</v>
+        <v>46158.28213052131</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28213052131</v>
+        <v>46158.29674297894</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29674297894</v>
+        <v>46158.29810946924</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810946924</v>
+        <v>46158.33383942563</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33383942563</v>
+        <v>46158.36852680119</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/26. С-Принтер (заправка картриджа, ремонт МФУ)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36852680119</v>
+        <v>46158.37284086864</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
